--- a/salidas/empresas/CMCSA.xlsx
+++ b/salidas/empresas/CMCSA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>5.751288414001465</v>
+        <v>5.751287937164307</v>
       </c>
       <c r="C2" t="n">
         <v>8.691034317016602</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>5.546621322631836</v>
+        <v>5.546621799468994</v>
       </c>
       <c r="C3" t="n">
         <v>8.381755828857422</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>5.40811014175415</v>
+        <v>5.408112049102783</v>
       </c>
       <c r="C4" t="n">
         <v>8.172446250915527</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>6.398356914520264</v>
+        <v>6.398359298706055</v>
       </c>
       <c r="C5" t="n">
         <v>9.668852806091309</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>6.642300128936768</v>
+        <v>6.642303943634033</v>
       </c>
       <c r="C6" t="n">
         <v>10.03748798370361</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>6.768405914306641</v>
+        <v>6.768415451049805</v>
       </c>
       <c r="C7" t="n">
         <v>10.22805404663086</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>7.107446670532227</v>
+        <v>7.107450485229492</v>
       </c>
       <c r="C8" t="n">
         <v>10.74039363861084</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>7.243889808654785</v>
+        <v>7.243894100189209</v>
       </c>
       <c r="C9" t="n">
         <v>10.94657897949219</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>7.628413677215576</v>
+        <v>7.628414154052734</v>
       </c>
       <c r="C10" t="n">
         <v>11.52764797210693</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>8.407794952392578</v>
+        <v>8.407792091369629</v>
       </c>
       <c r="C11" t="n">
         <v>12.70540523529053</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>8.364382743835449</v>
+        <v>8.364381790161133</v>
       </c>
       <c r="C12" t="n">
         <v>12.63980007171631</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>9.168567657470703</v>
+        <v>9.16856861114502</v>
       </c>
       <c r="C14" t="n">
         <v>13.85504531860352</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>7.975724220275879</v>
+        <v>7.975725173950195</v>
       </c>
       <c r="C15" t="n">
         <v>12.05248355865479</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>8.04704761505127</v>
+        <v>8.04704475402832</v>
       </c>
       <c r="C16" t="n">
         <v>12.16026210784912</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>8.499791145324707</v>
+        <v>8.49979305267334</v>
       </c>
       <c r="C18" t="n">
         <v>12.8444242477417</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>8.14627742767334</v>
+        <v>8.146276473999023</v>
       </c>
       <c r="C20" t="n">
         <v>12.31021595001221</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>8.090459823608398</v>
+        <v>8.090460777282715</v>
       </c>
       <c r="C21" t="n">
         <v>12.22586727142334</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>7.498172760009766</v>
+        <v>7.498177051544189</v>
       </c>
       <c r="C22" t="n">
         <v>11.33083438873291</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>6.527567386627197</v>
+        <v>6.527566432952881</v>
       </c>
       <c r="C23" t="n">
         <v>9.864105224609375</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>5.631381988525391</v>
+        <v>5.631382465362549</v>
       </c>
       <c r="C26" t="n">
         <v>8.509840965270996</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>6.059317111968994</v>
+        <v>6.059318542480469</v>
       </c>
       <c r="C27" t="n">
         <v>9.156514167785645</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>6.017271995544434</v>
+        <v>6.017271518707275</v>
       </c>
       <c r="C28" t="n">
         <v>9.062792778015137</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>6.393736839294434</v>
+        <v>6.393740177154541</v>
       </c>
       <c r="C29" t="n">
         <v>9.629802703857422</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>7.000446319580078</v>
+        <v>7.00044584274292</v>
       </c>
       <c r="C30" t="n">
         <v>10.54358005523682</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.902150630950928</v>
+        <v>5.902153968811035</v>
       </c>
       <c r="C31" t="n">
         <v>8.889410018920898</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.437644481658936</v>
+        <v>6.437645435333252</v>
       </c>
       <c r="C32" t="n">
         <v>9.662605285644531</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>6.612479209899902</v>
+        <v>6.612478256225586</v>
       </c>
       <c r="C33" t="n">
         <v>9.925023078918457</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>6.128562450408936</v>
+        <v>6.128563404083252</v>
       </c>
       <c r="C34" t="n">
         <v>9.198687553405762</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>4.937220096588135</v>
+        <v>4.937221527099609</v>
       </c>
       <c r="C35" t="n">
         <v>7.385191917419434</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>5.432194709777832</v>
+        <v>5.43219518661499</v>
       </c>
       <c r="C36" t="n">
         <v>8.125585556030273</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>5.288087844848633</v>
+        <v>5.288089275360107</v>
       </c>
       <c r="C37" t="n">
         <v>7.910027980804443</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>4.605612277984619</v>
+        <v>4.605613231658936</v>
       </c>
       <c r="C38" t="n">
         <v>6.865042209625244</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>4.288094520568848</v>
+        <v>4.288092136383057</v>
       </c>
       <c r="C40" t="n">
         <v>6.391753196716309</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>4.883159160614014</v>
+        <v>4.883156776428223</v>
       </c>
       <c r="C41" t="n">
         <v>7.244610786437988</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.349359512329102</v>
+        <v>4.349359035491943</v>
       </c>
       <c r="C42" t="n">
         <v>6.452671051025391</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>4.567300319671631</v>
+        <v>4.567298889160156</v>
       </c>
       <c r="C43" t="n">
         <v>6.776007175445557</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>4.716734409332275</v>
+        <v>4.716733932495117</v>
       </c>
       <c r="C44" t="n">
         <v>6.963449001312256</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>5.35790491104126</v>
+        <v>5.357908725738525</v>
       </c>
       <c r="C46" t="n">
         <v>7.910027980804443</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>4.623093128204346</v>
+        <v>4.623094081878662</v>
       </c>
       <c r="C47" t="n">
         <v>6.79475212097168</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>4.674107551574707</v>
+        <v>4.674106597900391</v>
       </c>
       <c r="C48" t="n">
         <v>6.869728088378906</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>5.375541687011719</v>
+        <v>5.375543117523193</v>
       </c>
       <c r="C49" t="n">
         <v>7.900656223297119</v>
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.075741291046143</v>
+        <v>5.075743198394775</v>
       </c>
       <c r="C50" t="n">
         <v>7.417994022369385</v>
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>5.271334171295166</v>
+        <v>5.271335601806641</v>
       </c>
       <c r="C51" t="n">
         <v>7.703843116760254</v>
@@ -1456,11 +1468,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>6.037665843963623</v>
+        <v>6.037668228149414</v>
       </c>
       <c r="C52" t="n">
         <v>8.82380485534668</v>
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>6.371158123016357</v>
+        <v>6.371160507202148</v>
       </c>
       <c r="C53" t="n">
         <v>9.264291763305664</v>
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>5.829756736755371</v>
+        <v>5.829757690429688</v>
       </c>
       <c r="C54" t="n">
         <v>8.477038383483887</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>5.597727298736572</v>
+        <v>5.59772777557373</v>
       </c>
       <c r="C55" t="n">
         <v>8.139643669128418</v>
@@ -1556,11 +1568,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.308262348175049</v>
+        <v>6.308263301849365</v>
       </c>
       <c r="C56" t="n">
         <v>9.123710632324219</v>
@@ -1581,7 +1593,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>5.857902050018311</v>
+        <v>5.857903003692627</v>
       </c>
       <c r="C58" t="n">
         <v>8.472352027893066</v>
@@ -1631,7 +1643,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>6.527739524841309</v>
+        <v>6.527740001678467</v>
       </c>
       <c r="C60" t="n">
         <v>9.390814781188965</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>7.156410217285156</v>
+        <v>7.156412124633789</v>
       </c>
       <c r="C61" t="n">
         <v>10.29522037506104</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.442666053771973</v>
+        <v>7.442667961120605</v>
       </c>
       <c r="C62" t="n">
         <v>10.66073131561279</v>
@@ -1731,7 +1743,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>8.087154388427734</v>
+        <v>8.087152481079102</v>
       </c>
       <c r="C64" t="n">
         <v>11.58388042449951</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>8.613212585449219</v>
+        <v>8.613214492797852</v>
       </c>
       <c r="C65" t="n">
         <v>12.2820987701416</v>
@@ -1818,7 +1830,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1847,7 +1859,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.928888320922852</v>
+        <v>7.928885936737061</v>
       </c>
       <c r="C68" t="n">
         <v>11.25585842132568</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>7.100347518920898</v>
+        <v>7.100348949432373</v>
       </c>
       <c r="C69" t="n">
         <v>10.07966327667236</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>6.905594825744629</v>
+        <v>6.905590057373047</v>
       </c>
       <c r="C70" t="n">
         <v>9.803187370300293</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>7.782773971557617</v>
+        <v>7.782769680023193</v>
       </c>
       <c r="C71" t="n">
         <v>10.98875427246094</v>
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>7.523900985717773</v>
+        <v>7.523900508880615</v>
       </c>
       <c r="C72" t="n">
         <v>10.62324333190918</v>
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>7.906550884246826</v>
+        <v>7.906554222106934</v>
       </c>
       <c r="C73" t="n">
         <v>11.1105899810791</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>8.863609313964844</v>
+        <v>8.863611221313477</v>
       </c>
       <c r="C74" t="n">
         <v>12.45548343658447</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.807329177856445</v>
+        <v>9.807328224182129</v>
       </c>
       <c r="C75" t="n">
         <v>13.78163146972656</v>
@@ -2108,11 +2120,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>10.00740814208984</v>
+        <v>10.00741291046143</v>
       </c>
       <c r="C76" t="n">
         <v>14.06279277801514</v>
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>10.17605972290039</v>
+        <v>10.17606449127197</v>
       </c>
       <c r="C77" t="n">
         <v>14.22211837768555</v>
@@ -2166,11 +2178,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.693242073059082</v>
+        <v>9.693240165710449</v>
       </c>
       <c r="C78" t="n">
         <v>13.54732894897461</v>
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>10.77581596374512</v>
+        <v>10.77581405639648</v>
       </c>
       <c r="C79" t="n">
         <v>14.98125553131104</v>
@@ -2224,11 +2236,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>10.9713134765625</v>
+        <v>10.97131061553955</v>
       </c>
       <c r="C80" t="n">
         <v>15.2530460357666</v>
@@ -2253,11 +2265,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>11.30163383483887</v>
+        <v>11.30163192749023</v>
       </c>
       <c r="C81" t="n">
         <v>15.71227741241455</v>
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>12.04653072357178</v>
+        <v>12.04653167724609</v>
       </c>
       <c r="C82" t="n">
         <v>16.74789047241211</v>
@@ -2311,11 +2323,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>12.70782947540283</v>
+        <v>12.7078332901001</v>
       </c>
       <c r="C83" t="n">
         <v>17.58669281005859</v>
@@ -2340,7 +2352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>12.70625495910645</v>
+        <v>12.70625686645508</v>
       </c>
       <c r="C85" t="n">
         <v>17.50702857971191</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>12.95113468170166</v>
+        <v>12.95112991333008</v>
       </c>
       <c r="C86" t="n">
         <v>17.84442329406738</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.53271007537842</v>
+        <v>13.5327091217041</v>
       </c>
       <c r="C87" t="n">
         <v>18.64573669433594</v>
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>14.2775411605835</v>
+        <v>14.27753448486328</v>
       </c>
       <c r="C88" t="n">
         <v>19.67197799682617</v>
@@ -2485,11 +2497,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>14.11181640625</v>
+        <v>14.11181163787842</v>
       </c>
       <c r="C89" t="n">
         <v>19.35332679748535</v>
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.7257080078125</v>
+        <v>13.72570610046387</v>
       </c>
       <c r="C90" t="n">
         <v>18.82380485534668</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>14.26557540893555</v>
+        <v>14.26557922363281</v>
       </c>
       <c r="C91" t="n">
         <v>19.56419944763184</v>
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.44924068450928</v>
+        <v>14.44924163818359</v>
       </c>
       <c r="C93" t="n">
         <v>19.72352409362793</v>
@@ -2630,7 +2642,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2659,7 +2671,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2688,7 +2700,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2717,7 +2729,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2746,11 +2758,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>18.84513854980469</v>
+        <v>18.84513473510742</v>
       </c>
       <c r="C98" t="n">
         <v>25.51546478271484</v>
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.8898983001709</v>
+        <v>17.88990211486816</v>
       </c>
       <c r="C99" t="n">
         <v>24.22211837768555</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.39781951904297</v>
+        <v>17.3978214263916</v>
       </c>
       <c r="C100" t="n">
         <v>23.44892120361328</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.99582481384277</v>
+        <v>17.99582290649414</v>
       </c>
       <c r="C101" t="n">
         <v>24.25491905212402</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>18.14880752563477</v>
+        <v>18.1488094329834</v>
       </c>
       <c r="C102" t="n">
         <v>24.46110534667969</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.74127578735352</v>
+        <v>18.74126243591309</v>
       </c>
       <c r="C103" t="n">
         <v>25.15463829040527</v>
@@ -2920,11 +2932,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>18.75872421264648</v>
+        <v>18.75872611999512</v>
       </c>
       <c r="C104" t="n">
         <v>25.17806816101074</v>
@@ -2949,11 +2961,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>19.1043643951416</v>
+        <v>19.10436820983887</v>
       </c>
       <c r="C105" t="n">
         <v>25.64198684692383</v>
@@ -2978,11 +2990,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>18.85439109802246</v>
+        <v>18.85439491271973</v>
       </c>
       <c r="C106" t="n">
         <v>25.20149993896484</v>
@@ -3007,7 +3019,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3036,11 +3048,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>19.99729537963867</v>
+        <v>19.9972972869873</v>
       </c>
       <c r="C108" t="n">
         <v>26.72914695739746</v>
@@ -3065,7 +3077,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3094,11 +3106,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>18.7069206237793</v>
+        <v>18.70691871643066</v>
       </c>
       <c r="C110" t="n">
         <v>24.90627861022949</v>
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>20.89966201782227</v>
+        <v>20.899658203125</v>
       </c>
       <c r="C111" t="n">
         <v>27.82567977905273</v>
@@ -3152,11 +3164,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.96466445922852</v>
+        <v>19.96466255187988</v>
       </c>
       <c r="C112" t="n">
         <v>26.46204376220703</v>
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.42074203491211</v>
+        <v>20.42073822021484</v>
       </c>
       <c r="C113" t="n">
         <v>27.06654167175293</v>
@@ -3210,7 +3222,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>21.34928512573242</v>
+        <v>21.34929084777832</v>
       </c>
       <c r="C115" t="n">
         <v>28.18181800842285</v>
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>22.15512084960938</v>
+        <v>22.15512275695801</v>
       </c>
       <c r="C116" t="n">
         <v>29.24554824829102</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>19.99675941467285</v>
+        <v>19.99676132202148</v>
       </c>
       <c r="C117" t="n">
         <v>26.39643859863281</v>
@@ -3326,11 +3338,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>20.1920166015625</v>
+        <v>20.19200897216797</v>
       </c>
       <c r="C118" t="n">
         <v>26.65417098999023</v>
@@ -3355,11 +3367,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>22.32471466064453</v>
+        <v>22.3247127532959</v>
       </c>
       <c r="C119" t="n">
         <v>29.34395408630371</v>
@@ -3384,11 +3396,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>21.69726371765137</v>
+        <v>21.6972541809082</v>
       </c>
       <c r="C120" t="n">
         <v>28.51921272277832</v>
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3442,11 +3454,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>19.94961166381836</v>
+        <v>19.94960975646973</v>
       </c>
       <c r="C122" t="n">
         <v>26.10590362548828</v>
@@ -3471,7 +3483,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3500,7 +3512,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>21.85513877868652</v>
+        <v>21.85514450073242</v>
       </c>
       <c r="C125" t="n">
         <v>28.47235107421875</v>
@@ -3558,11 +3570,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>22.76876258850098</v>
+        <v>22.76877021789551</v>
       </c>
       <c r="C126" t="n">
         <v>29.66260528564453</v>
@@ -3587,11 +3599,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>23.44859886169434</v>
+        <v>23.4485969543457</v>
       </c>
       <c r="C127" t="n">
         <v>30.54826545715332</v>
@@ -3616,11 +3628,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.29204177856445</v>
+        <v>24.29204559326172</v>
       </c>
       <c r="C128" t="n">
         <v>31.51358985900879</v>
@@ -3645,11 +3657,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>23.57321929931641</v>
+        <v>23.57321548461914</v>
       </c>
       <c r="C129" t="n">
         <v>30.58106803894043</v>
@@ -3674,11 +3686,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.96333694458008</v>
+        <v>23.96333312988281</v>
       </c>
       <c r="C130" t="n">
         <v>31.08716011047363</v>
@@ -3703,11 +3715,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>22.42357063293457</v>
+        <v>22.4235725402832</v>
       </c>
       <c r="C131" t="n">
         <v>28.96907234191895</v>
@@ -3732,11 +3744,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>25.21292495727539</v>
+        <v>25.21292114257812</v>
       </c>
       <c r="C132" t="n">
         <v>32.57263565063477</v>
@@ -3761,11 +3773,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>25.14471817016602</v>
+        <v>25.14472389221191</v>
       </c>
       <c r="C133" t="n">
         <v>32.35707473754883</v>
@@ -3790,11 +3802,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>27.4643726348877</v>
+        <v>27.46437644958496</v>
       </c>
       <c r="C134" t="n">
         <v>35.34207916259766</v>
@@ -3819,11 +3831,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>27.25316619873047</v>
+        <v>27.2531623840332</v>
       </c>
       <c r="C135" t="n">
         <v>35.07028961181641</v>
@@ -3848,11 +3860,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>27.37697792053223</v>
+        <v>27.37696838378906</v>
       </c>
       <c r="C136" t="n">
         <v>35.2296142578125</v>
@@ -3877,11 +3889,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>28.66274070739746</v>
+        <v>28.66273498535156</v>
       </c>
       <c r="C137" t="n">
         <v>36.72914886474609</v>
@@ -3906,11 +3918,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.49118614196777</v>
+        <v>30.49118232727051</v>
       </c>
       <c r="C138" t="n">
         <v>39.07216644287109</v>
@@ -3935,11 +3947,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>28.58144760131836</v>
+        <v>28.58144378662109</v>
       </c>
       <c r="C139" t="n">
         <v>36.47610092163086</v>
@@ -3964,7 +3976,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3993,11 +4005,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>29.82253074645996</v>
+        <v>29.82251739501953</v>
       </c>
       <c r="C141" t="n">
         <v>38.05998229980469</v>
@@ -4022,11 +4034,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>28.25832366943359</v>
+        <v>28.25832176208496</v>
       </c>
       <c r="C142" t="n">
         <v>36.06372833251953</v>
@@ -4051,11 +4063,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>26.56970596313477</v>
+        <v>26.56970024108887</v>
       </c>
       <c r="C143" t="n">
         <v>33.76757431030273</v>
@@ -4080,11 +4092,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>27.6832160949707</v>
+        <v>27.68322944641113</v>
       </c>
       <c r="C144" t="n">
         <v>35.18275451660156</v>
@@ -4109,11 +4121,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>29.53418159484863</v>
+        <v>29.53418350219727</v>
       </c>
       <c r="C145" t="n">
         <v>37.5351448059082</v>
@@ -4138,11 +4150,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.48723411560059</v>
+        <v>31.48723793029785</v>
       </c>
       <c r="C146" t="n">
         <v>39.85942077636719</v>
@@ -4167,11 +4179,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>26.80819702148438</v>
+        <v>26.80819511413574</v>
       </c>
       <c r="C147" t="n">
         <v>33.93627166748047</v>
@@ -4196,11 +4208,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>25.29787826538086</v>
+        <v>25.2978687286377</v>
       </c>
       <c r="C148" t="n">
         <v>32.02436828613281</v>
@@ -4225,11 +4237,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>23.37216758728027</v>
+        <v>23.37217140197754</v>
       </c>
       <c r="C149" t="n">
         <v>29.41893196105957</v>
@@ -4254,11 +4266,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>23.2158145904541</v>
+        <v>23.21581077575684</v>
       </c>
       <c r="C150" t="n">
         <v>29.22211837768555</v>
@@ -4283,11 +4295,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>24.42946243286133</v>
+        <v>24.42947387695312</v>
       </c>
       <c r="C151" t="n">
         <v>30.74976539611816</v>
@@ -4312,11 +4324,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>26.79602241516113</v>
+        <v>26.79602432250977</v>
       </c>
       <c r="C152" t="n">
         <v>33.53327178955078</v>
@@ -4341,11 +4353,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>27.70220184326172</v>
+        <v>27.70220947265625</v>
       </c>
       <c r="C153" t="n">
         <v>34.66728973388672</v>
@@ -4370,11 +4382,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>26.51892280578613</v>
+        <v>26.51892852783203</v>
       </c>
       <c r="C154" t="n">
         <v>33.18650436401367</v>
@@ -4399,11 +4411,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>28.71706199645996</v>
+        <v>28.71706390380859</v>
       </c>
       <c r="C155" t="n">
         <v>35.74507904052734</v>
@@ -4428,11 +4440,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>29.37211990356445</v>
+        <v>29.37211799621582</v>
       </c>
       <c r="C156" t="n">
         <v>36.56045150756836</v>
@@ -4457,11 +4469,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>25.7801456451416</v>
+        <v>25.78013801574707</v>
       </c>
       <c r="C157" t="n">
         <v>31.91190338134766</v>
@@ -4486,11 +4498,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.68809127807617</v>
+        <v>27.68809509277344</v>
       </c>
       <c r="C158" t="n">
         <v>34.27366256713867</v>
@@ -4515,11 +4527,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>29.27806091308594</v>
+        <v>29.27806282043457</v>
       </c>
       <c r="C159" t="n">
         <v>36.24179840087891</v>
@@ -4544,11 +4556,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>30.2699031829834</v>
+        <v>30.2698974609375</v>
       </c>
       <c r="C160" t="n">
         <v>37.46953964233398</v>
@@ -4573,11 +4585,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>33.13029479980469</v>
+        <v>33.13028335571289</v>
       </c>
       <c r="C161" t="n">
         <v>40.79662704467773</v>
@@ -4602,11 +4614,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>31.20473861694336</v>
+        <v>31.2047233581543</v>
       </c>
       <c r="C162" t="n">
         <v>38.42549133300781</v>
@@ -4631,11 +4643,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>32.17893218994141</v>
+        <v>32.17893600463867</v>
       </c>
       <c r="C163" t="n">
         <v>39.62511825561523</v>
@@ -4660,11 +4672,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>33.01865386962891</v>
+        <v>33.01864624023438</v>
       </c>
       <c r="C164" t="n">
         <v>40.45923233032227</v>
@@ -4689,11 +4701,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>33.85233306884766</v>
+        <v>33.85232925415039</v>
       </c>
       <c r="C165" t="n">
         <v>41.48078536987305</v>
@@ -4718,11 +4730,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>34.47952270507812</v>
+        <v>34.47951507568359</v>
       </c>
       <c r="C166" t="n">
         <v>42.24929809570312</v>
@@ -4747,11 +4759,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>34.44109344482422</v>
+        <v>34.44109725952148</v>
       </c>
       <c r="C167" t="n">
         <v>42.00562286376953</v>
@@ -4776,11 +4788,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>33.92624664306641</v>
+        <v>33.92625427246094</v>
       </c>
       <c r="C168" t="n">
         <v>41.37769317626953</v>
@@ -4805,11 +4817,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>34.55636215209961</v>
+        <v>34.55636596679688</v>
       </c>
       <c r="C169" t="n">
         <v>42.14620590209961</v>
@@ -4834,11 +4846,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>33.34530639648438</v>
+        <v>33.34531402587891</v>
       </c>
       <c r="C170" t="n">
         <v>40.47797775268555</v>
@@ -4863,7 +4875,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4892,7 +4904,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4921,11 +4933,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>29.24216270446777</v>
+        <v>29.24216842651367</v>
       </c>
       <c r="C173" t="n">
         <v>35.26710510253906</v>
@@ -4950,7 +4962,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4979,11 +4991,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>30.47122192382812</v>
+        <v>30.47121429443359</v>
       </c>
       <c r="C175" t="n">
         <v>36.53233337402344</v>
@@ -5008,11 +5020,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>33.45737075805664</v>
+        <v>33.45736694335938</v>
       </c>
       <c r="C176" t="n">
         <v>40.11246490478516</v>
@@ -5037,7 +5049,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5066,7 +5078,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5095,11 +5107,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>33.18622970581055</v>
+        <v>33.18622207641602</v>
       </c>
       <c r="C179" t="n">
         <v>39.58762741088867</v>
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>39.47150421142578</v>
+        <v>39.47149276733398</v>
       </c>
       <c r="C180" t="n">
         <v>47.08528518676758</v>
@@ -5153,11 +5165,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>41.16852951049805</v>
+        <v>41.16854095458984</v>
       </c>
       <c r="C181" t="n">
         <v>49.10965347290039</v>
@@ -5182,7 +5194,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5211,7 +5223,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5240,7 +5252,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5269,7 +5281,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5298,11 +5310,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>45.46315765380859</v>
+        <v>45.46316146850586</v>
       </c>
       <c r="C186" t="n">
         <v>53.73945617675781</v>
@@ -5327,11 +5339,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>45.20943832397461</v>
+        <v>45.20943450927734</v>
       </c>
       <c r="C187" t="n">
         <v>53.43954849243164</v>
@@ -5356,11 +5368,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>46.84500122070312</v>
+        <v>46.84499740600586</v>
       </c>
       <c r="C188" t="n">
         <v>55.13589477539062</v>
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>48.31811904907227</v>
+        <v>48.31811141967773</v>
       </c>
       <c r="C189" t="n">
         <v>56.86972808837891</v>
@@ -5414,11 +5426,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>44.53579711914062</v>
+        <v>44.53580474853516</v>
       </c>
       <c r="C190" t="n">
         <v>52.41799545288086</v>
@@ -5443,11 +5455,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>41.13364791870117</v>
+        <v>41.13366317749023</v>
       </c>
       <c r="C191" t="n">
         <v>48.2005615234375</v>
@@ -5472,7 +5484,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>40.25387954711914</v>
+        <v>40.25388336181641</v>
       </c>
       <c r="C193" t="n">
         <v>47.16963577270508</v>
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>40.1799201965332</v>
+        <v>40.17991256713867</v>
       </c>
       <c r="C194" t="n">
         <v>46.85098266601562</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>37.58377075195312</v>
+        <v>37.58378219604492</v>
       </c>
       <c r="C195" t="n">
         <v>43.82380676269531</v>
@@ -5588,11 +5600,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>37.63199615478516</v>
+        <v>37.63199996948242</v>
       </c>
       <c r="C196" t="n">
         <v>43.88003540039062</v>
@@ -5617,11 +5629,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>32.13783264160156</v>
+        <v>32.1378173828125</v>
       </c>
       <c r="C197" t="n">
         <v>37.26335525512695</v>
@@ -5646,11 +5658,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>35.79132080078125</v>
+        <v>35.79131317138672</v>
       </c>
       <c r="C198" t="n">
         <v>41.49953079223633</v>
@@ -5675,11 +5687,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>31.71751403808594</v>
+        <v>31.71751976013184</v>
       </c>
       <c r="C199" t="n">
         <v>36.77600860595703</v>
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>30.53184700012207</v>
+        <v>30.5318546295166</v>
       </c>
       <c r="C200" t="n">
         <v>35.16400909423828</v>
@@ -5733,11 +5745,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>29.44956016540527</v>
+        <v>29.4495677947998</v>
       </c>
       <c r="C201" t="n">
         <v>33.91752624511719</v>
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>23.86725044250488</v>
+        <v>23.86724853515625</v>
       </c>
       <c r="C202" t="n">
         <v>27.48828506469727</v>
@@ -5791,11 +5803,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>26.05808067321777</v>
+        <v>26.05808258056641</v>
       </c>
       <c r="C203" t="n">
         <v>29.7469539642334</v>
@@ -5820,11 +5832,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>30.08090400695801</v>
+        <v>30.08090972900391</v>
       </c>
       <c r="C204" t="n">
         <v>34.33926773071289</v>
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>28.70986557006836</v>
+        <v>28.70986747741699</v>
       </c>
       <c r="C205" t="n">
         <v>32.77413177490234</v>
@@ -5878,11 +5890,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>32.55714416503906</v>
+        <v>32.55714797973633</v>
       </c>
       <c r="C206" t="n">
         <v>36.87910079956055</v>
@@ -5907,11 +5919,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>30.75347709655762</v>
+        <v>30.75347900390625</v>
       </c>
       <c r="C207" t="n">
         <v>34.83599090576172</v>
@@ -5936,11 +5948,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>31.36572647094727</v>
+        <v>31.36573219299316</v>
       </c>
       <c r="C208" t="n">
         <v>35.52952194213867</v>
@@ -5965,7 +5977,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5994,7 +6006,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6023,7 +6035,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6052,7 +6064,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6081,11 +6093,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>39.25943374633789</v>
+        <v>39.25944519042969</v>
       </c>
       <c r="C213" t="n">
         <v>43.82380676269531</v>
@@ -6110,11 +6122,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>37.22761917114258</v>
+        <v>37.22762298583984</v>
       </c>
       <c r="C214" t="n">
         <v>41.55576324462891</v>
@@ -6139,7 +6151,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>35.40137100219727</v>
+        <v>35.40137481689453</v>
       </c>
       <c r="C216" t="n">
         <v>39.25960540771484</v>
@@ -6197,7 +6209,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6226,11 +6238,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>39.59294128417969</v>
+        <v>39.59294891357422</v>
       </c>
       <c r="C218" t="n">
         <v>43.61761856079102</v>
@@ -6255,11 +6267,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>36.45375823974609</v>
+        <v>36.45376205444336</v>
       </c>
       <c r="C219" t="n">
         <v>40.15932464599609</v>
@@ -6284,11 +6296,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>36.87911987304688</v>
+        <v>36.87912368774414</v>
       </c>
       <c r="C220" t="n">
         <v>40.6279296875</v>
@@ -6313,11 +6325,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>32.6607666015625</v>
+        <v>32.66077041625977</v>
       </c>
       <c r="C221" t="n">
         <v>35.71696472167969</v>
@@ -6342,7 +6354,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6371,7 +6383,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6400,11 +6412,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>35.65861511230469</v>
+        <v>35.65861892700195</v>
       </c>
       <c r="C224" t="n">
         <v>38.67853927612305</v>
@@ -6429,11 +6441,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>34.18975448608398</v>
+        <v>34.18975830078125</v>
       </c>
       <c r="C225" t="n">
         <v>37.08528518676758</v>
@@ -6458,7 +6470,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6487,7 +6499,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6516,7 +6528,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6545,11 +6557,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>32.67000198364258</v>
+        <v>32.66999816894531</v>
       </c>
       <c r="C229" t="n">
         <v>35.17338180541992</v>
@@ -6574,11 +6586,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>29.54751777648926</v>
+        <v>29.54751586914062</v>
       </c>
       <c r="C230" t="n">
         <v>31.5463924407959</v>
@@ -6603,7 +6615,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6632,7 +6644,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6661,11 +6673,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>30.29378509521484</v>
+        <v>30.29378700256348</v>
       </c>
       <c r="C233" t="n">
         <v>32.05248260498047</v>
@@ -6690,7 +6702,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6719,11 +6731,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>31.61360359191895</v>
+        <v>31.61360168457031</v>
       </c>
       <c r="C235" t="n">
         <v>33.44892120361328</v>
@@ -6748,11 +6760,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>29.70439338684082</v>
+        <v>29.70439529418945</v>
       </c>
       <c r="C236" t="n">
         <v>31.14339256286621</v>
@@ -6777,11 +6789,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>30.36588287353516</v>
+        <v>30.36588096618652</v>
       </c>
       <c r="C237" t="n">
         <v>31.8369255065918</v>
@@ -6806,7 +6818,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6835,7 +6847,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6864,7 +6876,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6893,7 +6905,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6922,7 +6934,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6951,7 +6963,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6980,7 +6992,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7009,7 +7021,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7038,7 +7050,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7067,7 +7079,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7096,7 +7108,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7154,32 +7166,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>22.54999923706055</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="C250" t="n">
-        <v>22.54999923706055</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="D250" t="n">
-        <v>495145000</v>
+        <v>531086700</v>
       </c>
       <c r="E250" t="n">
         <v>3.353008434864105</v>
       </c>
       <c r="F250" t="n">
-        <v>6.725303462582695</v>
+        <v>6.600042794602608</v>
       </c>
       <c r="G250" t="n">
         <v>3564000000</v>
       </c>
       <c r="H250" t="n">
-        <v>80368197280.88379</v>
+        <v>78871317008.97217</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1389295735129069</v>
+        <v>0.1490142255892256</v>
       </c>
     </row>
   </sheetData>
@@ -7211,75 +7223,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7516,7 +7528,7 @@
       <c r="I7" t="n">
         <v>0.5904404873477038</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7529,13 +7541,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7562,7 +7574,7 @@
       <c r="I8" t="n">
         <v>0.6091846298031866</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7608,7 +7620,7 @@
       <c r="I9" t="n">
         <v>0.5998125585754452</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7621,13 +7633,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7654,7 +7666,7 @@
       <c r="I10" t="n">
         <v>0.5904404873477038</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7667,13 +7679,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7700,7 +7712,7 @@
       <c r="I11" t="n">
         <v>0.6044985941893158</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7713,13 +7725,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7746,7 +7758,7 @@
       <c r="I12" t="n">
         <v>0.6185567010309279</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K12" t="n">
@@ -7759,13 +7771,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7792,7 +7804,7 @@
       <c r="I13" t="n">
         <v>0.6466729147141519</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="K13" t="n">
@@ -7805,13 +7817,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7838,7 +7850,7 @@
       <c r="I14" t="n">
         <v>0.6560449859418932</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7851,13 +7863,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7884,7 +7896,7 @@
       <c r="I15" t="n">
         <v>0.7075913776944706</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K15" t="n">
@@ -7897,13 +7909,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7930,7 +7942,7 @@
       <c r="I16" t="n">
         <v>0.7591377694470478</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7943,13 +7955,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7976,7 +7988,7 @@
       <c r="I17" t="n">
         <v>0.8200562324273665</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="K17" t="n">
@@ -7989,13 +8001,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8022,7 +8034,7 @@
       <c r="I18" t="n">
         <v>1.030927835051547</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="K18" t="n">
@@ -8035,13 +8047,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8068,7 +8080,7 @@
       <c r="I19" t="n">
         <v>1.073102155576382</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K19" t="n">
@@ -8081,13 +8093,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8114,7 +8126,7 @@
       <c r="I20" t="n">
         <v>1.115276476101219</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8127,13 +8139,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8160,7 +8172,7 @@
       <c r="I21" t="n">
         <v>1.185567010309279</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K21" t="n">
@@ -8173,13 +8185,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8206,7 +8218,7 @@
       <c r="I22" t="n">
         <v>1.12464854732896</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K22" t="n">
@@ -8219,13 +8231,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8252,7 +8264,7 @@
       <c r="I23" t="n">
         <v>1.19962511715089</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="K23" t="n">
@@ -8265,13 +8277,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41751</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8298,7 +8310,7 @@
       <c r="I24" t="n">
         <v>1.279287722586692</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41751</v>
       </c>
       <c r="K24" t="n">
@@ -8311,13 +8323,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8344,7 +8356,7 @@
       <c r="I25" t="n">
         <v>1.330834114339269</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K25" t="n">
@@ -8357,13 +8369,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8390,7 +8402,7 @@
       <c r="I26" t="n">
         <v>1.490159325210872</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K26" t="n">
@@ -8403,13 +8415,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8436,7 +8448,7 @@
       <c r="I27" t="n">
         <v>1.499531396438613</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K27" t="n">
@@ -8449,13 +8461,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8482,7 +8494,7 @@
       <c r="I28" t="n">
         <v>1.54639175257732</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K28" t="n">
@@ -8495,13 +8507,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8528,7 +8540,7 @@
       <c r="I29" t="n">
         <v>1.583880037488285</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K29" t="n">
@@ -8541,13 +8553,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8574,7 +8586,7 @@
       <c r="I30" t="n">
         <v>1.494845360824742</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K30" t="n">
@@ -8587,13 +8599,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8620,7 +8632,7 @@
       <c r="I31" t="n">
         <v>1.518275538894096</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="K31" t="n">
@@ -8633,13 +8645,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8666,7 +8678,7 @@
       <c r="I32" t="n">
         <v>1.54639175257732</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="K32" t="n">
@@ -8679,13 +8691,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8712,7 +8724,7 @@
       <c r="I33" t="n">
         <v>1.541705716963449</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K33" t="n">
@@ -8725,13 +8737,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8758,7 +8770,7 @@
       <c r="I34" t="n">
         <v>1.597938144329897</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="K34" t="n">
@@ -8771,13 +8783,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8804,7 +8816,7 @@
       <c r="I35" t="n">
         <v>1.672914714151827</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="K35" t="n">
@@ -8817,13 +8829,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8850,7 +8862,7 @@
       <c r="I36" t="n">
         <v>1.76194939081537</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8863,13 +8875,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8896,7 +8908,7 @@
       <c r="I37" t="n">
         <v>1.860356138706654</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K37" t="n">
@@ -8909,13 +8921,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8942,7 +8954,7 @@
       <c r="I38" t="n">
         <v>1.944704779756326</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8955,13 +8967,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8988,7 +9000,7 @@
       <c r="I39" t="n">
         <v>4.470477975632615</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="K39" t="n">
@@ -9001,13 +9013,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9034,7 +9046,7 @@
       <c r="I40" t="n">
         <v>4.592314901593252</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="K40" t="n">
@@ -9047,13 +9059,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9080,7 +9092,7 @@
       <c r="I41" t="n">
         <v>4.751640112464854</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -9093,13 +9105,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9126,7 +9138,7 @@
       <c r="I42" t="n">
         <v>4.817244611059044</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K42" t="n">
@@ -9139,13 +9151,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9172,7 +9184,7 @@
       <c r="I43" t="n">
         <v>2.361761949390815</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="K43" t="n">
@@ -9185,13 +9197,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9218,7 +9230,7 @@
       <c r="I44" t="n">
         <v>2.46485473289597</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K44" t="n">
@@ -9231,13 +9243,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9264,7 +9276,7 @@
       <c r="I45" t="n">
         <v>2.455482661668229</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K45" t="n">
@@ -9277,13 +9289,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9310,7 +9322,7 @@
       <c r="I46" t="n">
         <v>2.530459231490159</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K46" t="n">
@@ -9323,13 +9335,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9356,7 +9368,7 @@
       <c r="I47" t="n">
         <v>2.652296157450797</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="K47" t="n">
@@ -9369,13 +9381,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9402,7 +9414,7 @@
       <c r="I48" t="n">
         <v>2.361761949390816</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K48" t="n">
@@ -9415,13 +9427,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9448,7 +9460,7 @@
       <c r="I49" t="n">
         <v>2.333645735707591</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K49" t="n">
@@ -9461,13 +9473,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9494,7 +9506,7 @@
       <c r="I50" t="n">
         <v>2.089971883786317</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K50" t="n">
@@ -9507,13 +9519,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9540,7 +9552,7 @@
       <c r="I51" t="n">
         <v>2.136832239925023</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="K51" t="n">
@@ -9553,13 +9565,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9586,7 +9598,7 @@
       <c r="I52" t="n">
         <v>2.371134020618557</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9599,13 +9611,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9632,7 +9644,7 @@
       <c r="I53" t="n">
         <v>2.511715089034677</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9645,13 +9657,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9678,7 +9690,7 @@
       <c r="I54" t="n">
         <v>2.905342080599812</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9691,13 +9703,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9724,7 +9736,7 @@
       <c r="I55" t="n">
         <v>2.849109653233365</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="K55" t="n">
@@ -9737,13 +9749,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9770,7 +9782,7 @@
       <c r="I56" t="n">
         <v>2.914714151827554</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9783,13 +9795,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9816,7 +9828,7 @@
       <c r="I57" t="n">
         <v>2.877225866916589</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9829,13 +9841,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9862,7 +9874,7 @@
       <c r="I58" t="n">
         <v>1.087160262417995</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9875,13 +9887,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9908,7 +9920,7 @@
       <c r="I59" t="n">
         <v>1.134020618556701</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="K59" t="n">
@@ -9921,13 +9933,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9954,7 +9966,7 @@
       <c r="I60" t="n">
         <v>1.255857544517338</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9967,13 +9979,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10000,7 +10012,7 @@
       <c r="I61" t="n">
         <v>1.499531396438613</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -10013,13 +10025,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10046,7 +10058,7 @@
       <c r="I62" t="n">
         <v>3.402061855670103</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K62" t="n">
@@ -10059,13 +10071,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10092,7 +10104,7 @@
       <c r="I63" t="n">
         <v>3.477038425492034</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="K63" t="n">
@@ -10105,13 +10117,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10138,7 +10150,7 @@
       <c r="I64" t="n">
         <v>3.533270852858482</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10151,13 +10163,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10184,7 +10196,7 @@
       <c r="I65" t="n">
         <v>3.514526710402999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="K65" t="n">
@@ -10197,13 +10209,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10230,7 +10242,7 @@
       <c r="I66" t="n">
         <v>3.477038425492034</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K66" t="n">
@@ -10243,13 +10255,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10276,7 +10288,7 @@
       <c r="I67" t="n">
         <v>3.880037488284911</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K67" t="n">
@@ -10289,13 +10301,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10322,7 +10334,7 @@
       <c r="I68" t="n">
         <v>3.80506091846298</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K68" t="n">
@@ -10335,13 +10347,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10368,7 +10380,7 @@
       <c r="I69" t="n">
         <v>5.660731021555764</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K69" t="n">
@@ -10381,13 +10393,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10414,7 +10426,7 @@
       <c r="I70" t="n">
         <v>5.623242736644798</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10427,13 +10439,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10460,7 +10472,7 @@
       <c r="I71" t="n">
         <v>5.39</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="K71" t="n">
@@ -10473,13 +10485,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10506,7 +10518,7 @@
       <c r="I72" t="n">
         <v>5.155885660731022</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K72" t="n">
@@ -10519,13 +10531,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10552,7 +10564,7 @@
       <c r="I73" t="n">
         <v>3.353008434864105</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K73" t="n">
@@ -10590,57 +10602,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40121</v>
       </c>
       <c r="C2" t="n">
@@ -10670,10 +10682,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40232</v>
       </c>
       <c r="C3" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="C4" t="n">
@@ -10740,10 +10752,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="C5" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C6" t="n">
@@ -10814,10 +10826,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C7" t="n">
@@ -10851,10 +10863,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10888,10 +10900,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C10" t="n">
@@ -10962,10 +10974,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="C11" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40758</v>
       </c>
       <c r="C12" t="n">
@@ -11036,10 +11048,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="C13" t="n">
@@ -11073,10 +11085,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C14" t="n">
@@ -11110,10 +11122,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C15" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="C16" t="n">
@@ -11184,10 +11196,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C17" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C18" t="n">
@@ -11258,10 +11270,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C19" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C20" t="n">
@@ -11332,10 +11344,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C21" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="C22" t="n">
@@ -11406,10 +11418,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41751</v>
       </c>
       <c r="C23" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C24" t="n">
@@ -11480,10 +11492,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C25" t="n">
@@ -11517,10 +11529,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C26" t="n">
@@ -11554,10 +11566,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C27" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C28" t="n">
@@ -11628,10 +11640,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C29" t="n">
@@ -11665,10 +11677,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="C30" t="n">
@@ -11702,10 +11714,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42487</v>
       </c>
       <c r="C31" t="n">
@@ -11739,10 +11751,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C32" t="n">
@@ -11776,10 +11788,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42669</v>
       </c>
       <c r="C33" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="C34" t="n">
@@ -11850,10 +11862,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C35" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C36" t="n">
@@ -11924,10 +11936,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C37" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="C38" t="n">
@@ -11998,10 +12010,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43215</v>
       </c>
       <c r="C39" t="n">
@@ -12035,10 +12047,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C40" t="n">
@@ -12072,10 +12084,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C41" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="C42" t="n">
@@ -12146,10 +12158,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C43" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C44" t="n">
@@ -12220,10 +12232,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C45" t="n">
@@ -12257,10 +12269,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43860</v>
       </c>
       <c r="C46" t="n">
@@ -12294,10 +12306,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C47" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C48" t="n">
@@ -12368,10 +12380,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C49" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="C50" t="n">
@@ -12442,10 +12454,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C51" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C52" t="n">
@@ -12516,10 +12528,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C53" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="C54" t="n">
@@ -12590,10 +12602,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C55" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C56" t="n">
@@ -12664,10 +12676,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C57" t="n">
@@ -12701,10 +12713,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="C58" t="n">
@@ -12738,10 +12750,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C59" t="n">
@@ -12775,10 +12787,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C60" t="n">
@@ -12812,10 +12824,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C61" t="n">
@@ -12849,10 +12861,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="C62" t="n">
@@ -12886,10 +12898,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C63" t="n">
@@ -12923,10 +12935,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="C64" t="n">
@@ -12960,10 +12972,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C65" t="n">
@@ -12997,10 +13009,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C66" t="n">
@@ -13034,10 +13046,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C67" t="n">
@@ -13071,10 +13083,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C68" t="n">
@@ -13108,10 +13120,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C69" t="n">
@@ -13145,10 +13157,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C70" t="n">
@@ -13182,10 +13194,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C71" t="n">
@@ -13219,10 +13231,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C72" t="n">
@@ -13274,12 +13286,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CMCSA.xlsx
+++ b/salidas/empresas/CMCSA.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>5.751287937164307</v>
+        <v>5.751288414001465</v>
       </c>
       <c r="C2" t="n">
         <v>8.691034317016602</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>5.546621799468994</v>
+        <v>5.546623229980469</v>
       </c>
       <c r="C3" t="n">
         <v>8.381755828857422</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>6.398359298706055</v>
+        <v>6.398358345031738</v>
       </c>
       <c r="C5" t="n">
         <v>9.668852806091309</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>6.642303943634033</v>
+        <v>6.642302513122559</v>
       </c>
       <c r="C6" t="n">
         <v>10.03748798370361</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>6.768415451049805</v>
+        <v>6.76840877532959</v>
       </c>
       <c r="C7" t="n">
         <v>10.22805404663086</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>7.107450485229492</v>
+        <v>7.107448101043701</v>
       </c>
       <c r="C8" t="n">
         <v>10.74039363861084</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>7.243894100189209</v>
+        <v>7.24389123916626</v>
       </c>
       <c r="C9" t="n">
         <v>10.94657897949219</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>7.628414154052734</v>
+        <v>7.628414630889893</v>
       </c>
       <c r="C10" t="n">
         <v>11.52764797210693</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>8.407792091369629</v>
+        <v>8.407795906066895</v>
       </c>
       <c r="C11" t="n">
         <v>12.70540523529053</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>8.364381790161133</v>
+        <v>8.364380836486816</v>
       </c>
       <c r="C12" t="n">
         <v>12.63980007171631</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>8.75096607208252</v>
+        <v>8.750971794128418</v>
       </c>
       <c r="C13" t="n">
         <v>13.2239933013916</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>9.16856861114502</v>
+        <v>9.16856575012207</v>
       </c>
       <c r="C14" t="n">
         <v>13.85504531860352</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>7.975725173950195</v>
+        <v>7.97572660446167</v>
       </c>
       <c r="C15" t="n">
         <v>12.05248355865479</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>8.04704475402832</v>
+        <v>8.047046661376953</v>
       </c>
       <c r="C16" t="n">
         <v>12.16026210784912</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>8.71996021270752</v>
+        <v>8.719959259033203</v>
       </c>
       <c r="C19" t="n">
         <v>13.17713165283203</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>8.146276473999023</v>
+        <v>8.146278381347656</v>
       </c>
       <c r="C20" t="n">
         <v>12.31021595001221</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>8.090460777282715</v>
+        <v>8.090459823608398</v>
       </c>
       <c r="C21" t="n">
         <v>12.22586727142334</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>7.498177051544189</v>
+        <v>7.49817419052124</v>
       </c>
       <c r="C22" t="n">
         <v>11.33083438873291</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>6.527566432952881</v>
+        <v>6.527567386627197</v>
       </c>
       <c r="C23" t="n">
         <v>9.864105224609375</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>6.369417190551758</v>
+        <v>6.369417667388916</v>
       </c>
       <c r="C24" t="n">
         <v>9.625117301940918</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>5.662392616271973</v>
+        <v>5.662389278411865</v>
       </c>
       <c r="C25" t="n">
         <v>8.556700706481934</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>5.631382465362549</v>
+        <v>5.631381988525391</v>
       </c>
       <c r="C26" t="n">
         <v>8.509840965270996</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>6.059318542480469</v>
+        <v>6.059319019317627</v>
       </c>
       <c r="C27" t="n">
         <v>9.156514167785645</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>6.017271518707275</v>
+        <v>6.017270565032959</v>
       </c>
       <c r="C28" t="n">
         <v>9.062792778015137</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>6.393740177154541</v>
+        <v>6.393741130828857</v>
       </c>
       <c r="C29" t="n">
         <v>9.629802703857422</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>7.00044584274292</v>
+        <v>7.000442504882812</v>
       </c>
       <c r="C30" t="n">
         <v>10.54358005523682</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.902153968811035</v>
+        <v>5.902152538299561</v>
       </c>
       <c r="C31" t="n">
         <v>8.889410018920898</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.437645435333252</v>
+        <v>6.437646389007568</v>
       </c>
       <c r="C32" t="n">
         <v>9.662605285644531</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>6.612478256225586</v>
+        <v>6.612481117248535</v>
       </c>
       <c r="C33" t="n">
         <v>9.925023078918457</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>4.937221527099609</v>
+        <v>4.937218189239502</v>
       </c>
       <c r="C35" t="n">
         <v>7.385191917419434</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>5.43219518661499</v>
+        <v>5.432193756103516</v>
       </c>
       <c r="C36" t="n">
         <v>8.125585556030273</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>5.288089275360107</v>
+        <v>5.288087844848633</v>
       </c>
       <c r="C37" t="n">
         <v>7.910027980804443</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>4.605613231658936</v>
+        <v>4.605612754821777</v>
       </c>
       <c r="C38" t="n">
         <v>6.865042209625244</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>4.105754375457764</v>
+        <v>4.105754852294922</v>
       </c>
       <c r="C39" t="n">
         <v>6.1199631690979</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>4.288092136383057</v>
+        <v>4.288094043731689</v>
       </c>
       <c r="C40" t="n">
         <v>6.391753196716309</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>4.883156776428223</v>
+        <v>4.883157253265381</v>
       </c>
       <c r="C41" t="n">
         <v>7.244610786437988</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.349359035491943</v>
+        <v>4.349358081817627</v>
       </c>
       <c r="C42" t="n">
         <v>6.452671051025391</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>4.567298889160156</v>
+        <v>4.567300319671631</v>
       </c>
       <c r="C43" t="n">
         <v>6.776007175445557</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>4.716733932495117</v>
+        <v>4.716734886169434</v>
       </c>
       <c r="C44" t="n">
         <v>6.963449001312256</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>5.357908725738525</v>
+        <v>5.357905864715576</v>
       </c>
       <c r="C46" t="n">
         <v>7.910027980804443</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>4.623094081878662</v>
+        <v>4.623095512390137</v>
       </c>
       <c r="C47" t="n">
         <v>6.79475212097168</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>4.674106597900391</v>
+        <v>4.674107551574707</v>
       </c>
       <c r="C48" t="n">
         <v>6.869728088378906</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>5.375543117523193</v>
+        <v>5.375542640686035</v>
       </c>
       <c r="C49" t="n">
         <v>7.900656223297119</v>
@@ -1447,7 +1447,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>5.271335601806641</v>
+        <v>5.271333694458008</v>
       </c>
       <c r="C51" t="n">
         <v>7.703843116760254</v>
@@ -1472,7 +1472,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>6.037668228149414</v>
+        <v>6.037665843963623</v>
       </c>
       <c r="C52" t="n">
         <v>8.82380485534668</v>
@@ -1497,7 +1497,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>6.371160507202148</v>
+        <v>6.37116003036499</v>
       </c>
       <c r="C53" t="n">
         <v>9.264291763305664</v>
@@ -1522,7 +1522,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>5.829757690429688</v>
+        <v>5.829755306243896</v>
       </c>
       <c r="C54" t="n">
         <v>8.477038383483887</v>
@@ -1547,7 +1547,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>5.59772777557373</v>
+        <v>5.597725391387939</v>
       </c>
       <c r="C55" t="n">
         <v>8.139643669128418</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.308263301849365</v>
+        <v>6.308263778686523</v>
       </c>
       <c r="C56" t="n">
         <v>9.123710632324219</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>5.540384292602539</v>
+        <v>5.540383815765381</v>
       </c>
       <c r="C57" t="n">
         <v>8.013120651245117</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>5.857903003692627</v>
+        <v>5.857900619506836</v>
       </c>
       <c r="C58" t="n">
         <v>8.472352027893066</v>
@@ -1647,7 +1647,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>6.719924449920654</v>
+        <v>6.719925880432129</v>
       </c>
       <c r="C59" t="n">
         <v>9.667290687561035</v>
@@ -1672,7 +1672,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>6.527740001678467</v>
+        <v>6.527738571166992</v>
       </c>
       <c r="C60" t="n">
         <v>9.390814781188965</v>
@@ -1697,7 +1697,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>7.156412124633789</v>
+        <v>7.156410217285156</v>
       </c>
       <c r="C61" t="n">
         <v>10.29522037506104</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.442667961120605</v>
+        <v>7.442665576934814</v>
       </c>
       <c r="C62" t="n">
         <v>10.66073131561279</v>
@@ -1747,7 +1747,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>8.427389144897461</v>
+        <v>8.427390098571777</v>
       </c>
       <c r="C63" t="n">
         <v>12.07122802734375</v>
@@ -1776,7 +1776,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>8.087152481079102</v>
+        <v>8.087154388427734</v>
       </c>
       <c r="C64" t="n">
         <v>11.58388042449951</v>
@@ -1805,7 +1805,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>8.613214492797852</v>
+        <v>8.613212585449219</v>
       </c>
       <c r="C65" t="n">
         <v>12.2820987701416</v>
@@ -1834,7 +1834,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>8.294450759887695</v>
+        <v>8.294451713562012</v>
       </c>
       <c r="C66" t="n">
         <v>11.82755374908447</v>
@@ -1863,7 +1863,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>8.327313423156738</v>
+        <v>8.327312469482422</v>
       </c>
       <c r="C67" t="n">
         <v>11.87441444396973</v>
@@ -1892,7 +1892,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.928885936737061</v>
+        <v>7.928885459899902</v>
       </c>
       <c r="C68" t="n">
         <v>11.25585842132568</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>7.100348949432373</v>
+        <v>7.100349426269531</v>
       </c>
       <c r="C69" t="n">
         <v>10.07966327667236</v>
@@ -1950,7 +1950,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>6.905590057373047</v>
+        <v>6.905591487884521</v>
       </c>
       <c r="C70" t="n">
         <v>9.803187370300293</v>
@@ -1979,7 +1979,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>7.782769680023193</v>
+        <v>7.782771110534668</v>
       </c>
       <c r="C71" t="n">
         <v>10.98875427246094</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>7.523900508880615</v>
+        <v>7.523898601531982</v>
       </c>
       <c r="C72" t="n">
         <v>10.62324333190918</v>
@@ -2037,7 +2037,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>7.906554222106934</v>
+        <v>7.906553268432617</v>
       </c>
       <c r="C73" t="n">
         <v>11.1105899810791</v>
@@ -2066,7 +2066,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>8.863611221313477</v>
+        <v>8.863615036010742</v>
       </c>
       <c r="C74" t="n">
         <v>12.45548343658447</v>
@@ -2095,7 +2095,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.807328224182129</v>
+        <v>9.807332992553711</v>
       </c>
       <c r="C75" t="n">
         <v>13.78163146972656</v>
@@ -2124,7 +2124,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>10.00741291046143</v>
+        <v>10.00740909576416</v>
       </c>
       <c r="C76" t="n">
         <v>14.06279277801514</v>
@@ -2153,7 +2153,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>10.17606449127197</v>
+        <v>10.17605876922607</v>
       </c>
       <c r="C77" t="n">
         <v>14.22211837768555</v>
@@ -2182,7 +2182,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.693240165710449</v>
+        <v>9.693241119384766</v>
       </c>
       <c r="C78" t="n">
         <v>13.54732894897461</v>
@@ -2211,7 +2211,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>10.77581405639648</v>
+        <v>10.77581787109375</v>
       </c>
       <c r="C79" t="n">
         <v>14.98125553131104</v>
@@ -2240,7 +2240,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>10.97131061553955</v>
+        <v>10.97131252288818</v>
       </c>
       <c r="C80" t="n">
         <v>15.2530460357666</v>
@@ -2269,7 +2269,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>11.30163192749023</v>
+        <v>11.30162906646729</v>
       </c>
       <c r="C81" t="n">
         <v>15.71227741241455</v>
@@ -2298,7 +2298,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>12.04653167724609</v>
+        <v>12.04653263092041</v>
       </c>
       <c r="C82" t="n">
         <v>16.74789047241211</v>
@@ -2327,7 +2327,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>12.7078332901001</v>
+        <v>12.70782661437988</v>
       </c>
       <c r="C83" t="n">
         <v>17.58669281005859</v>
@@ -2356,7 +2356,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>12.59609127044678</v>
+        <v>12.59608936309814</v>
       </c>
       <c r="C84" t="n">
         <v>17.43205261230469</v>
@@ -2385,7 +2385,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>12.70625686645508</v>
+        <v>12.70625877380371</v>
       </c>
       <c r="C85" t="n">
         <v>17.50702857971191</v>
@@ -2414,7 +2414,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>12.95112991333008</v>
+        <v>12.95113182067871</v>
       </c>
       <c r="C86" t="n">
         <v>17.84442329406738</v>
@@ -2443,7 +2443,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>13.5327091217041</v>
+        <v>13.53270626068115</v>
       </c>
       <c r="C87" t="n">
         <v>18.64573669433594</v>
@@ -2472,7 +2472,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>14.27753448486328</v>
+        <v>14.2775354385376</v>
       </c>
       <c r="C88" t="n">
         <v>19.67197799682617</v>
@@ -2501,7 +2501,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>14.11181163787842</v>
+        <v>14.11181735992432</v>
       </c>
       <c r="C89" t="n">
         <v>19.35332679748535</v>
@@ -2530,7 +2530,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.72570610046387</v>
+        <v>13.72570133209229</v>
       </c>
       <c r="C90" t="n">
         <v>18.82380485534668</v>
@@ -2559,7 +2559,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>14.26557922363281</v>
+        <v>14.26557731628418</v>
       </c>
       <c r="C91" t="n">
         <v>19.56419944763184</v>
@@ -2617,7 +2617,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.44924163818359</v>
+        <v>14.44923305511475</v>
       </c>
       <c r="C93" t="n">
         <v>19.72352409362793</v>
@@ -2646,7 +2646,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>15.55722522735596</v>
+        <v>15.55722904205322</v>
       </c>
       <c r="C94" t="n">
         <v>21.14339256286621</v>
@@ -2704,7 +2704,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>17.19500923156738</v>
+        <v>17.19501113891602</v>
       </c>
       <c r="C96" t="n">
         <v>23.36926078796387</v>
@@ -2762,7 +2762,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>18.84513473510742</v>
+        <v>18.84514236450195</v>
       </c>
       <c r="C98" t="n">
         <v>25.51546478271484</v>
@@ -2791,7 +2791,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>17.88990211486816</v>
+        <v>17.8898983001709</v>
       </c>
       <c r="C99" t="n">
         <v>24.22211837768555</v>
@@ -2820,7 +2820,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.3978214263916</v>
+        <v>17.39781761169434</v>
       </c>
       <c r="C100" t="n">
         <v>23.44892120361328</v>
@@ -2849,7 +2849,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.99582290649414</v>
+        <v>17.99582862854004</v>
       </c>
       <c r="C101" t="n">
         <v>24.25491905212402</v>
@@ -2878,7 +2878,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>18.1488094329834</v>
+        <v>18.14879989624023</v>
       </c>
       <c r="C102" t="n">
         <v>24.46110534667969</v>
@@ -2907,7 +2907,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.74126243591309</v>
+        <v>18.74127006530762</v>
       </c>
       <c r="C103" t="n">
         <v>25.15463829040527</v>
@@ -2936,7 +2936,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>18.75872611999512</v>
+        <v>18.75872802734375</v>
       </c>
       <c r="C104" t="n">
         <v>25.17806816101074</v>
@@ -2965,7 +2965,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>19.10436820983887</v>
+        <v>19.1043643951416</v>
       </c>
       <c r="C105" t="n">
         <v>25.64198684692383</v>
@@ -2994,7 +2994,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>18.85439491271973</v>
+        <v>18.85439682006836</v>
       </c>
       <c r="C106" t="n">
         <v>25.20149993896484</v>
@@ -3023,7 +3023,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>19.40481567382812</v>
+        <v>19.40480995178223</v>
       </c>
       <c r="C107" t="n">
         <v>25.93720626831055</v>
@@ -3081,7 +3081,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>20.33736610412598</v>
+        <v>20.33736228942871</v>
       </c>
       <c r="C109" t="n">
         <v>27.18369293212891</v>
@@ -3110,7 +3110,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>18.70691871643066</v>
+        <v>18.7069206237793</v>
       </c>
       <c r="C110" t="n">
         <v>24.90627861022949</v>
@@ -3168,7 +3168,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.96466255187988</v>
+        <v>19.96467399597168</v>
       </c>
       <c r="C112" t="n">
         <v>26.46204376220703</v>
@@ -3197,7 +3197,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>20.42073822021484</v>
+        <v>20.42074203491211</v>
       </c>
       <c r="C113" t="n">
         <v>27.06654167175293</v>
@@ -3226,7 +3226,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>20.66822242736816</v>
+        <v>20.66822052001953</v>
       </c>
       <c r="C114" t="n">
         <v>27.39456367492676</v>
@@ -3255,7 +3255,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>21.34929084777832</v>
+        <v>21.34928894042969</v>
       </c>
       <c r="C115" t="n">
         <v>28.18181800842285</v>
@@ -3284,7 +3284,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>22.15512275695801</v>
+        <v>22.15511894226074</v>
       </c>
       <c r="C116" t="n">
         <v>29.24554824829102</v>
@@ -3313,7 +3313,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>19.99676132202148</v>
+        <v>19.99676513671875</v>
       </c>
       <c r="C117" t="n">
         <v>26.39643859863281</v>
@@ -3342,7 +3342,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>20.19200897216797</v>
+        <v>20.1920051574707</v>
       </c>
       <c r="C118" t="n">
         <v>26.65417098999023</v>
@@ -3371,7 +3371,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>22.3247127532959</v>
+        <v>22.32471656799316</v>
       </c>
       <c r="C119" t="n">
         <v>29.34395408630371</v>
@@ -3400,7 +3400,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>21.6972541809082</v>
+        <v>21.6972599029541</v>
       </c>
       <c r="C120" t="n">
         <v>28.51921272277832</v>
@@ -3429,7 +3429,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>20.11791038513184</v>
+        <v>20.11791610717773</v>
       </c>
       <c r="C121" t="n">
         <v>26.44329833984375</v>
@@ -3487,7 +3487,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.67296409606934</v>
+        <v>20.67296600341797</v>
       </c>
       <c r="C123" t="n">
         <v>27.0524845123291</v>
@@ -3516,7 +3516,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>21.87259292602539</v>
+        <v>21.87259483337402</v>
       </c>
       <c r="C124" t="n">
         <v>28.62230682373047</v>
@@ -3632,7 +3632,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.29204559326172</v>
+        <v>24.29204940795898</v>
       </c>
       <c r="C128" t="n">
         <v>31.51358985900879</v>
@@ -3661,7 +3661,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>23.57321548461914</v>
+        <v>23.57321929931641</v>
       </c>
       <c r="C129" t="n">
         <v>30.58106803894043</v>
@@ -3690,7 +3690,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.96333312988281</v>
+        <v>23.96333694458008</v>
       </c>
       <c r="C130" t="n">
         <v>31.08716011047363</v>
@@ -3719,7 +3719,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>22.4235725402832</v>
+        <v>22.42357635498047</v>
       </c>
       <c r="C131" t="n">
         <v>28.96907234191895</v>
@@ -3748,7 +3748,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>25.21292114257812</v>
+        <v>25.21291923522949</v>
       </c>
       <c r="C132" t="n">
         <v>32.57263565063477</v>
@@ -3806,7 +3806,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>27.46437644958496</v>
+        <v>27.46437072753906</v>
       </c>
       <c r="C134" t="n">
         <v>35.34207916259766</v>
@@ -3835,7 +3835,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>27.2531623840332</v>
+        <v>27.25317192077637</v>
       </c>
       <c r="C135" t="n">
         <v>35.07028961181641</v>
@@ -3864,7 +3864,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>27.37696838378906</v>
+        <v>27.37697410583496</v>
       </c>
       <c r="C136" t="n">
         <v>35.2296142578125</v>
@@ -3893,7 +3893,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>28.66273498535156</v>
+        <v>28.66274452209473</v>
       </c>
       <c r="C137" t="n">
         <v>36.72914886474609</v>
@@ -3922,7 +3922,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.49118232727051</v>
+        <v>30.49118041992188</v>
       </c>
       <c r="C138" t="n">
         <v>39.07216644287109</v>
@@ -3951,7 +3951,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>28.58144378662109</v>
+        <v>28.58144950866699</v>
       </c>
       <c r="C139" t="n">
         <v>36.47610092163086</v>
@@ -4009,7 +4009,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>29.82251739501953</v>
+        <v>29.82251930236816</v>
       </c>
       <c r="C141" t="n">
         <v>38.05998229980469</v>
@@ -4038,7 +4038,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>28.25832176208496</v>
+        <v>28.25832557678223</v>
       </c>
       <c r="C142" t="n">
         <v>36.06372833251953</v>
@@ -4096,7 +4096,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>27.68322944641113</v>
+        <v>27.68321990966797</v>
       </c>
       <c r="C144" t="n">
         <v>35.18275451660156</v>
@@ -4125,7 +4125,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>29.53418350219727</v>
+        <v>29.53417587280273</v>
       </c>
       <c r="C145" t="n">
         <v>37.5351448059082</v>
@@ -4154,7 +4154,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.48723793029785</v>
+        <v>31.48723602294922</v>
       </c>
       <c r="C146" t="n">
         <v>39.85942077636719</v>
@@ -4183,7 +4183,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>26.80819511413574</v>
+        <v>26.80819129943848</v>
       </c>
       <c r="C147" t="n">
         <v>33.93627166748047</v>
@@ -4212,7 +4212,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>25.2978687286377</v>
+        <v>25.29787635803223</v>
       </c>
       <c r="C148" t="n">
         <v>32.02436828613281</v>
@@ -4241,7 +4241,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>23.37217140197754</v>
+        <v>23.37217330932617</v>
       </c>
       <c r="C149" t="n">
         <v>29.41893196105957</v>
@@ -4270,7 +4270,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>23.21581077575684</v>
+        <v>23.21580696105957</v>
       </c>
       <c r="C150" t="n">
         <v>29.22211837768555</v>
@@ -4299,7 +4299,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>24.42947387695312</v>
+        <v>24.42946434020996</v>
       </c>
       <c r="C151" t="n">
         <v>30.74976539611816</v>
@@ -4357,7 +4357,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>27.70220947265625</v>
+        <v>27.70220184326172</v>
       </c>
       <c r="C153" t="n">
         <v>34.66728973388672</v>
@@ -4386,7 +4386,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>26.51892852783203</v>
+        <v>26.51892280578613</v>
       </c>
       <c r="C154" t="n">
         <v>33.18650436401367</v>
@@ -4415,7 +4415,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>28.71706390380859</v>
+        <v>28.71706581115723</v>
       </c>
       <c r="C155" t="n">
         <v>35.74507904052734</v>
@@ -4444,7 +4444,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>29.37211799621582</v>
+        <v>29.37212181091309</v>
       </c>
       <c r="C156" t="n">
         <v>36.56045150756836</v>
@@ -4473,7 +4473,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>25.78013801574707</v>
+        <v>25.78014373779297</v>
       </c>
       <c r="C157" t="n">
         <v>31.91190338134766</v>
@@ -4502,7 +4502,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.68809509277344</v>
+        <v>27.6880931854248</v>
       </c>
       <c r="C158" t="n">
         <v>34.27366256713867</v>
@@ -4531,7 +4531,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>29.27806282043457</v>
+        <v>29.27806663513184</v>
       </c>
       <c r="C159" t="n">
         <v>36.24179840087891</v>
@@ -4560,7 +4560,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>30.2698974609375</v>
+        <v>30.26990509033203</v>
       </c>
       <c r="C160" t="n">
         <v>37.46953964233398</v>
@@ -4589,7 +4589,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>33.13028335571289</v>
+        <v>33.13029861450195</v>
       </c>
       <c r="C161" t="n">
         <v>40.79662704467773</v>
@@ -4618,7 +4618,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>31.2047233581543</v>
+        <v>31.20473289489746</v>
       </c>
       <c r="C162" t="n">
         <v>38.42549133300781</v>
@@ -4647,7 +4647,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>32.17893600463867</v>
+        <v>32.17893218994141</v>
       </c>
       <c r="C163" t="n">
         <v>39.62511825561523</v>
@@ -4705,7 +4705,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>33.85232925415039</v>
+        <v>33.85233306884766</v>
       </c>
       <c r="C165" t="n">
         <v>41.48078536987305</v>
@@ -4763,7 +4763,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>34.44109725952148</v>
+        <v>34.44110107421875</v>
       </c>
       <c r="C167" t="n">
         <v>42.00562286376953</v>
@@ -4792,7 +4792,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>33.92625427246094</v>
+        <v>33.92624282836914</v>
       </c>
       <c r="C168" t="n">
         <v>41.37769317626953</v>
@@ -4821,7 +4821,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>34.55636596679688</v>
+        <v>34.55636215209961</v>
       </c>
       <c r="C169" t="n">
         <v>42.14620590209961</v>
@@ -4850,7 +4850,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>33.34531402587891</v>
+        <v>33.34531784057617</v>
       </c>
       <c r="C170" t="n">
         <v>40.47797775268555</v>
@@ -4879,7 +4879,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>31.21442413330078</v>
+        <v>31.21442794799805</v>
       </c>
       <c r="C171" t="n">
         <v>37.89128494262695</v>
@@ -4908,7 +4908,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>26.71659851074219</v>
+        <v>26.71659660339355</v>
       </c>
       <c r="C172" t="n">
         <v>32.2211799621582</v>
@@ -4937,7 +4937,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>29.24216842651367</v>
+        <v>29.24216079711914</v>
       </c>
       <c r="C173" t="n">
         <v>35.26710510253906</v>
@@ -4966,7 +4966,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>30.77304458618164</v>
+        <v>30.77304077148438</v>
       </c>
       <c r="C174" t="n">
         <v>37.1134033203125</v>
@@ -4995,7 +4995,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>30.47121429443359</v>
+        <v>30.47122383117676</v>
       </c>
       <c r="C175" t="n">
         <v>36.53233337402344</v>
@@ -5024,7 +5024,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>33.45736694335938</v>
+        <v>33.45737075805664</v>
       </c>
       <c r="C176" t="n">
         <v>40.11246490478516</v>
@@ -5053,7 +5053,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>35.02862167358398</v>
+        <v>35.02861785888672</v>
       </c>
       <c r="C177" t="n">
         <v>41.99625015258789</v>
@@ -5111,7 +5111,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>33.18622207641602</v>
+        <v>33.18622589111328</v>
       </c>
       <c r="C179" t="n">
         <v>39.58762741088867</v>
@@ -5140,7 +5140,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>39.47149276733398</v>
+        <v>39.47150421142578</v>
       </c>
       <c r="C180" t="n">
         <v>47.08528518676758</v>
@@ -5169,7 +5169,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>41.16854095458984</v>
+        <v>41.16851806640625</v>
       </c>
       <c r="C181" t="n">
         <v>49.10965347290039</v>
@@ -5198,7 +5198,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>39.12326431274414</v>
+        <v>39.12325286865234</v>
       </c>
       <c r="C182" t="n">
         <v>46.45735549926758</v>
@@ -5227,7 +5227,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>41.60940933227539</v>
+        <v>41.60941696166992</v>
       </c>
       <c r="C183" t="n">
         <v>49.40956115722656</v>
@@ -5285,7 +5285,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>44.5196418762207</v>
+        <v>44.51963806152344</v>
       </c>
       <c r="C185" t="n">
         <v>52.62417984008789</v>
@@ -5314,7 +5314,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>45.46316146850586</v>
+        <v>45.46315002441406</v>
       </c>
       <c r="C186" t="n">
         <v>53.73945617675781</v>
@@ -5372,7 +5372,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>46.84499740600586</v>
+        <v>46.84500885009766</v>
       </c>
       <c r="C188" t="n">
         <v>55.13589477539062</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>48.31811141967773</v>
+        <v>48.318115234375</v>
       </c>
       <c r="C189" t="n">
         <v>56.86972808837891</v>
@@ -5430,7 +5430,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>44.53580474853516</v>
+        <v>44.53579711914062</v>
       </c>
       <c r="C190" t="n">
         <v>52.41799545288086</v>
@@ -5459,7 +5459,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>41.13366317749023</v>
+        <v>41.1336555480957</v>
       </c>
       <c r="C191" t="n">
         <v>48.2005615234375</v>
@@ -5488,7 +5488,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>39.97394943237305</v>
+        <v>39.97394561767578</v>
       </c>
       <c r="C192" t="n">
         <v>46.84161376953125</v>
@@ -5517,7 +5517,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>40.25388336181641</v>
+        <v>40.25389099121094</v>
       </c>
       <c r="C193" t="n">
         <v>47.16963577270508</v>
@@ -5546,7 +5546,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>40.17991256713867</v>
+        <v>40.17990875244141</v>
       </c>
       <c r="C194" t="n">
         <v>46.85098266601562</v>
@@ -5575,7 +5575,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>37.58378219604492</v>
+        <v>37.58378982543945</v>
       </c>
       <c r="C195" t="n">
         <v>43.82380676269531</v>
@@ -5604,7 +5604,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>37.63199996948242</v>
+        <v>37.63200378417969</v>
       </c>
       <c r="C196" t="n">
         <v>43.88003540039062</v>
@@ -5633,7 +5633,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>32.1378173828125</v>
+        <v>32.13782119750977</v>
       </c>
       <c r="C197" t="n">
         <v>37.26335525512695</v>
@@ -5662,7 +5662,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>35.79131317138672</v>
+        <v>35.79131698608398</v>
       </c>
       <c r="C198" t="n">
         <v>41.49953079223633</v>
@@ -5691,7 +5691,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>31.71751976013184</v>
+        <v>31.71751594543457</v>
       </c>
       <c r="C199" t="n">
         <v>36.77600860595703</v>
@@ -5720,7 +5720,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>30.5318546295166</v>
+        <v>30.53184127807617</v>
       </c>
       <c r="C200" t="n">
         <v>35.16400909423828</v>
@@ -5778,7 +5778,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>23.86724853515625</v>
+        <v>23.86724662780762</v>
       </c>
       <c r="C202" t="n">
         <v>27.48828506469727</v>
@@ -5807,7 +5807,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>26.05808258056641</v>
+        <v>26.05807876586914</v>
       </c>
       <c r="C203" t="n">
         <v>29.7469539642334</v>
@@ -5836,7 +5836,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>30.08090972900391</v>
+        <v>30.08091354370117</v>
       </c>
       <c r="C204" t="n">
         <v>34.33926773071289</v>
@@ -5865,7 +5865,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>28.70986747741699</v>
+        <v>28.70986557006836</v>
       </c>
       <c r="C205" t="n">
         <v>32.77413177490234</v>
@@ -5894,7 +5894,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>32.55714797973633</v>
+        <v>32.55715179443359</v>
       </c>
       <c r="C206" t="n">
         <v>36.87910079956055</v>
@@ -5923,7 +5923,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>30.75347900390625</v>
+        <v>30.75346946716309</v>
       </c>
       <c r="C207" t="n">
         <v>34.83599090576172</v>
@@ -5981,7 +5981,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>34.49160003662109</v>
+        <v>34.49159622192383</v>
       </c>
       <c r="C209" t="n">
         <v>38.77225875854492</v>
@@ -6068,7 +6068,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>38.00004577636719</v>
+        <v>38.00004959106445</v>
       </c>
       <c r="C212" t="n">
         <v>42.41799545288086</v>
@@ -6126,7 +6126,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>37.22762298583984</v>
+        <v>37.22762680053711</v>
       </c>
       <c r="C214" t="n">
         <v>41.55576324462891</v>
@@ -6155,7 +6155,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>34.89431381225586</v>
+        <v>34.89430999755859</v>
       </c>
       <c r="C215" t="n">
         <v>38.69728088378906</v>
@@ -6213,7 +6213,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>37.05777740478516</v>
+        <v>37.05777359008789</v>
       </c>
       <c r="C217" t="n">
         <v>41.09653091430664</v>
@@ -6242,7 +6242,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>39.59294891357422</v>
+        <v>39.59294509887695</v>
       </c>
       <c r="C218" t="n">
         <v>43.61761856079102</v>
@@ -6271,7 +6271,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>36.45376205444336</v>
+        <v>36.45375442504883</v>
       </c>
       <c r="C219" t="n">
         <v>40.15932464599609</v>
@@ -6300,7 +6300,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>36.87912368774414</v>
+        <v>36.87912750244141</v>
       </c>
       <c r="C220" t="n">
         <v>40.6279296875</v>
@@ -6329,7 +6329,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>32.66077041625977</v>
+        <v>32.66077423095703</v>
       </c>
       <c r="C221" t="n">
         <v>35.71696472167969</v>
@@ -6358,7 +6358,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>34.30623626708984</v>
+        <v>34.30622863769531</v>
       </c>
       <c r="C222" t="n">
         <v>37.51639938354492</v>
@@ -6387,7 +6387,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>33.56063461303711</v>
+        <v>33.56064224243164</v>
       </c>
       <c r="C223" t="n">
         <v>36.70103073120117</v>
@@ -6416,7 +6416,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>35.65861892700195</v>
+        <v>35.65861129760742</v>
       </c>
       <c r="C224" t="n">
         <v>38.67853927612305</v>
@@ -6474,7 +6474,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>36.09062194824219</v>
+        <v>36.09063339233398</v>
       </c>
       <c r="C226" t="n">
         <v>39.14714050292969</v>
@@ -6503,7 +6503,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>38.014892578125</v>
+        <v>38.01489639282227</v>
       </c>
       <c r="C227" t="n">
         <v>40.92783355712891</v>
@@ -6561,7 +6561,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>32.66999816894531</v>
+        <v>32.67000198364258</v>
       </c>
       <c r="C229" t="n">
         <v>35.17338180541992</v>
@@ -6619,7 +6619,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>31.49628448486328</v>
+        <v>31.49628257751465</v>
       </c>
       <c r="C231" t="n">
         <v>33.62699127197266</v>
@@ -6648,7 +6648,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>32.39166259765625</v>
+        <v>32.39165878295898</v>
       </c>
       <c r="C232" t="n">
         <v>34.58294296264648</v>
@@ -6706,7 +6706,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>30.62152671813965</v>
+        <v>30.62152481079102</v>
       </c>
       <c r="C234" t="n">
         <v>32.39925003051758</v>
@@ -6735,7 +6735,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>31.61360168457031</v>
+        <v>31.61360359191895</v>
       </c>
       <c r="C235" t="n">
         <v>33.44892120361328</v>
@@ -6764,7 +6764,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>29.70439529418945</v>
+        <v>29.70439338684082</v>
       </c>
       <c r="C236" t="n">
         <v>31.14339256286621</v>
@@ -6793,7 +6793,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>30.36588096618652</v>
+        <v>30.36588287353516</v>
       </c>
       <c r="C237" t="n">
         <v>31.8369255065918</v>
